--- a/ui/public/sample/sample-ktx.xlsx
+++ b/ui/public/sample/sample-ktx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vlute\kiemketaisan\ui\public\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F889E8AA-8763-4203-909C-5AE7CBBA943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A536A672-A983-47EC-ABF1-1F0C8769F960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3D5B14DE-4EE5-4AF0-A39E-8713899E4B3B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{A3EABE27-5327-408F-BFBC-010F01E2E4AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,90 +35,40 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Admin</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{4A34A936-39DB-41D7-9759-8F70254072AD}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Times New Roman"/>
-            <family val="1"/>
-          </rPr>
-          <t xml:space="preserve">Tham chiếu danh mục Hemis
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{5C6E9647-79F7-4D21-962B-F3066B5060CA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Times New Roman"/>
-            <family val="1"/>
-          </rPr>
-          <t xml:space="preserve">Tham chiếu danh mục Hemis
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Mã ký túc xá</t>
+    <t>MÃ PHÒNG</t>
   </si>
   <si>
-    <t>Hình thức sở hữu</t>
+    <t>TÊN PHÒNG</t>
   </si>
   <si>
-    <t>Tổng số chỗ ở KTX</t>
+    <t>DIỆN TÍCH</t>
   </si>
   <si>
-    <t>Tổng diện tích</t>
+    <t>NĂM SỬ DỤNG</t>
   </si>
   <si>
-    <t>Tình trạng CSVC</t>
+    <t>SỨC CHỨA</t>
   </si>
   <si>
-    <t xml:space="preserve">Số phòng ở cho sinh viên </t>
+    <t>KTX_A</t>
   </si>
   <si>
-    <t>Năm đưa vào sử dụng</t>
+    <t>Ký túc xá A</t>
   </si>
   <si>
-    <t>Tình trạng sử dụng</t>
+    <t>360</t>
   </si>
   <si>
-    <t>Ngày chuyển trạng thái</t>
+    <t>KTX_B</t>
   </si>
   <si>
-    <t>Địa chỉ</t>
+    <t>720</t>
   </si>
   <si>
-    <t>KTX_A1</t>
-  </si>
-  <si>
-    <t>Sở hữu</t>
-  </si>
-  <si>
-    <t>Kiên cố</t>
-  </si>
-  <si>
-    <t>Đang sử dụng</t>
-  </si>
-  <si>
-    <t>Số 1 Xuân Thủy, Phường Dịch Vọng Hậu, Cầu Giấy, Hà Nội</t>
+    <t>Ký túc xá B</t>
   </si>
 </sst>
 </file>
@@ -136,14 +86,14 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -161,12 +111,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,18 +125,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -209,50 +153,45 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,111 +526,596 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4707D6A7-63A4-45AF-96E0-C26E14F13ACD}">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5543B858-F816-42BF-955C-5C3B426D08EF}">
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" s="11">
+        <v>3056</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="E2" s="11">
+        <v>2006</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11">
+        <v>6000</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1200</v>
-      </c>
-      <c r="D2" s="5">
-        <v>2650</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="6">
-        <f>C2/8</f>
-        <v>150</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2022</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="E3" s="11">
+        <v>2016</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="7"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="8"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+    </row>
+    <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="8"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+    </row>
+    <row r="56" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="8"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+    </row>
+    <row r="59" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>